--- a/EDEPA_2026/EDEPA_Version_2/Datos/base_hermana_B.xlsx
+++ b/EDEPA_2026/EDEPA_Version_2/Datos/base_hermana_B.xlsx
@@ -1,37 +1,57 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Datos" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+  <si>
+    <t>Edad</t>
+  </si>
+  <si>
+    <t>Visitas</t>
+  </si>
+  <si>
+    <t>Peso</t>
+  </si>
+  <si>
+    <t>Estatura</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +66,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,1437 +382,1425 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D101"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Edad</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Visitas</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Peso</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Estatura</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
         <v>76.5</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>9</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>69.7</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>1.74</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:4">
+      <c r="A3">
         <v>40.3</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>6</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>62.2</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>1.69</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:4">
+      <c r="A4">
         <v>66.7</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>6</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>67.5</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>1.69</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:4">
+      <c r="A5">
         <v>54.7</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>8</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>73.7</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>1.69</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:4">
+      <c r="A6">
         <v>36.2</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>0</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>45.9</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>1.61</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:4">
+      <c r="A7">
         <v>75.2</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>4</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>56.8</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>1.56</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:4">
+      <c r="A8">
         <v>71.90000000000001</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>0</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>50.4</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>1.6</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:4">
+      <c r="A9">
         <v>40.6</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>1</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>37.8</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>1.67</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:4">
+      <c r="A10">
         <v>78.3</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>5</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>84.90000000000001</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>1.45</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" spans="1:4">
+      <c r="A11">
         <v>31.9</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>6</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>91.8</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>1.64</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" spans="1:4">
+      <c r="A12">
         <v>67.90000000000001</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>9</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>88.09999999999999</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>1.58</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" spans="1:4">
+      <c r="A13">
         <v>60.2</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>4</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>42.9</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>1.67</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:4">
+      <c r="A14">
         <v>47.2</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>8</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>76</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>1.6</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" spans="1:4">
+      <c r="A15">
         <v>19.9</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>4</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>80.3</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>1.69</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="16" spans="1:4">
+      <c r="A16">
         <v>73.5</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>0</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>61.2</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>1.66</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" spans="1:4">
+      <c r="A17">
         <v>53.6</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>0</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>82.40000000000001</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>1.81</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" spans="1:4">
+      <c r="A18">
         <v>42.2</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>9</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>52.9</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>1.65</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" spans="1:4">
+      <c r="A19">
         <v>40</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>4</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>53.5</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>1.66</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" spans="1:4">
+      <c r="A20">
         <v>58.4</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>2</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>57.2</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>1.68</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" spans="1:4">
+      <c r="A21">
         <v>39.5</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>0</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>58.9</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>1.5</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" spans="1:4">
+      <c r="A22">
         <v>49.5</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>2</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>54.6</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>1.57</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
+    <row r="23" spans="1:4">
+      <c r="A23">
         <v>41</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>9</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>84.59999999999999</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>1.82</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
+    <row r="24" spans="1:4">
+      <c r="A24">
         <v>21.4</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24">
         <v>1</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>53.6</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>1.73</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="25" spans="1:4">
+      <c r="A25">
         <v>33.5</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25">
         <v>4</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>62.8</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>1.69</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
+    <row r="26" spans="1:4">
+      <c r="A26">
         <v>70.09999999999999</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>3</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>60.2</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>1.79</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
+    <row r="27" spans="1:4">
+      <c r="A27">
         <v>68.7</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27">
         <v>7</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>103.4</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>1.66</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
+    <row r="28" spans="1:4">
+      <c r="A28">
         <v>59.4</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28">
         <v>4</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>56.2</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28">
         <v>1.66</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="n">
+    <row r="29" spans="1:4">
+      <c r="A29">
         <v>47.2</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29">
         <v>6</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>77.09999999999999</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29">
         <v>1.65</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="n">
+    <row r="30" spans="1:4">
+      <c r="A30">
         <v>78.09999999999999</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30">
         <v>0</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>97.59999999999999</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30">
         <v>1.5</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="n">
+    <row r="31" spans="1:4">
+      <c r="A31">
         <v>70.09999999999999</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31">
         <v>4</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31">
         <v>51.9</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31">
         <v>1.77</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="n">
+    <row r="32" spans="1:4">
+      <c r="A32">
         <v>33.2</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32">
         <v>5</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32">
         <v>57.3</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32">
         <v>1.66</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="n">
+    <row r="33" spans="1:4">
+      <c r="A33">
         <v>53.2</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33">
         <v>3</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33">
         <v>64.90000000000001</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33">
         <v>1.67</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="n">
+    <row r="34" spans="1:4">
+      <c r="A34">
         <v>77.3</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34">
         <v>7</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34">
         <v>49.8</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34">
         <v>1.65</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="n">
+    <row r="35" spans="1:4">
+      <c r="A35">
         <v>66.7</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35">
         <v>0</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35">
         <v>88.5</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35">
         <v>1.62</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="n">
+    <row r="36" spans="1:4">
+      <c r="A36">
         <v>40.9</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36">
         <v>0</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36">
         <v>62.7</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36">
         <v>1.45</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="n">
+    <row r="37" spans="1:4">
+      <c r="A37">
         <v>47.1</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37">
         <v>7</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37">
         <v>85.90000000000001</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37">
         <v>1.7</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="n">
+    <row r="38" spans="1:4">
+      <c r="A38">
         <v>50.1</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38">
         <v>6</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38">
         <v>78</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38">
         <v>1.9</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="n">
+    <row r="39" spans="1:4">
+      <c r="A39">
         <v>73.90000000000001</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39">
         <v>1</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39">
         <v>70.3</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39">
         <v>1.78</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="n">
+    <row r="40" spans="1:4">
+      <c r="A40">
         <v>62.3</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40">
         <v>6</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40">
         <v>84.5</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40">
         <v>1.65</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="n">
+    <row r="41" spans="1:4">
+      <c r="A41">
         <v>42.7</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B41">
         <v>2</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C41">
         <v>65.40000000000001</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41">
         <v>1.59</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="n">
+    <row r="42" spans="1:4">
+      <c r="A42">
         <v>46.6</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B42">
         <v>5</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42">
         <v>85.90000000000001</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42">
         <v>1.68</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="n">
+    <row r="43" spans="1:4">
+      <c r="A43">
         <v>23.7</v>
       </c>
-      <c r="B43" t="n">
+      <c r="B43">
         <v>10</v>
       </c>
-      <c r="C43" t="n">
+      <c r="C43">
         <v>50.1</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43">
         <v>1.72</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="n">
+    <row r="44" spans="1:4">
+      <c r="A44">
         <v>48.5</v>
       </c>
-      <c r="B44" t="n">
+      <c r="B44">
         <v>2</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C44">
         <v>58.7</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44">
         <v>1.67</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="n">
+    <row r="45" spans="1:4">
+      <c r="A45">
         <v>32.2</v>
       </c>
-      <c r="B45" t="n">
+      <c r="B45">
         <v>4</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C45">
         <v>88.2</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45">
         <v>1.76</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="n">
+    <row r="46" spans="1:4">
+      <c r="A46">
         <v>23.8</v>
       </c>
-      <c r="B46" t="n">
+      <c r="B46">
         <v>8</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C46">
         <v>38.3</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46">
         <v>1.58</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="n">
+    <row r="47" spans="1:4">
+      <c r="A47">
         <v>23.7</v>
       </c>
-      <c r="B47" t="n">
+      <c r="B47">
         <v>3</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47">
         <v>77.09999999999999</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47">
         <v>1.79</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="n">
+    <row r="48" spans="1:4">
+      <c r="A48">
         <v>31.4</v>
       </c>
-      <c r="B48" t="n">
+      <c r="B48">
         <v>8</v>
       </c>
-      <c r="C48" t="n">
+      <c r="C48">
         <v>63.7</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48">
         <v>1.7</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="n">
+    <row r="49" spans="1:4">
+      <c r="A49">
         <v>61.3</v>
       </c>
-      <c r="B49" t="n">
+      <c r="B49">
         <v>7</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C49">
         <v>61.7</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49">
         <v>1.63</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="n">
+    <row r="50" spans="1:4">
+      <c r="A50">
         <v>29.1</v>
       </c>
-      <c r="B50" t="n">
+      <c r="B50">
         <v>5</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C50">
         <v>59.4</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50">
         <v>1.65</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="n">
+    <row r="51" spans="1:4">
+      <c r="A51">
         <v>53.2</v>
       </c>
-      <c r="B51" t="n">
+      <c r="B51">
         <v>2</v>
       </c>
-      <c r="C51" t="n">
+      <c r="C51">
         <v>89.40000000000001</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51">
         <v>1.71</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="n">
+    <row r="52" spans="1:4">
+      <c r="A52">
         <v>55.4</v>
       </c>
-      <c r="B52" t="n">
+      <c r="B52">
         <v>8</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C52">
         <v>46.9</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52">
         <v>1.76</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="n">
+    <row r="53" spans="1:4">
+      <c r="A53">
         <v>77.90000000000001</v>
       </c>
-      <c r="B53" t="n">
+      <c r="B53">
         <v>4</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C53">
         <v>82.5</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D53">
         <v>1.69</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="n">
+    <row r="54" spans="1:4">
+      <c r="A54">
         <v>46.4</v>
       </c>
-      <c r="B54" t="n">
+      <c r="B54">
         <v>10</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C54">
         <v>77.2</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54">
         <v>1.74</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="n">
+    <row r="55" spans="1:4">
+      <c r="A55">
         <v>66</v>
       </c>
-      <c r="B55" t="n">
+      <c r="B55">
         <v>3</v>
       </c>
-      <c r="C55" t="n">
+      <c r="C55">
         <v>63.6</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55">
         <v>1.92</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="n">
+    <row r="56" spans="1:4">
+      <c r="A56">
         <v>20.2</v>
       </c>
-      <c r="B56" t="n">
+      <c r="B56">
         <v>1</v>
       </c>
-      <c r="C56" t="n">
+      <c r="C56">
         <v>68.7</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56">
         <v>1.52</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="n">
+    <row r="57" spans="1:4">
+      <c r="A57">
         <v>58</v>
       </c>
-      <c r="B57" t="n">
+      <c r="B57">
         <v>7</v>
       </c>
-      <c r="C57" t="n">
+      <c r="C57">
         <v>80.59999999999999</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D57">
         <v>1.48</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="n">
+    <row r="58" spans="1:4">
+      <c r="A58">
         <v>78.8</v>
       </c>
-      <c r="B58" t="n">
+      <c r="B58">
         <v>4</v>
       </c>
-      <c r="C58" t="n">
+      <c r="C58">
         <v>61</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D58">
         <v>1.69</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="n">
+    <row r="59" spans="1:4">
+      <c r="A59">
         <v>20.9</v>
       </c>
-      <c r="B59" t="n">
+      <c r="B59">
         <v>0</v>
       </c>
-      <c r="C59" t="n">
+      <c r="C59">
         <v>47.2</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D59">
         <v>1.58</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="n">
+    <row r="60" spans="1:4">
+      <c r="A60">
         <v>74.3</v>
       </c>
-      <c r="B60" t="n">
+      <c r="B60">
         <v>9</v>
       </c>
-      <c r="C60" t="n">
+      <c r="C60">
         <v>74.2</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D60">
         <v>1.69</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="n">
+    <row r="61" spans="1:4">
+      <c r="A61">
         <v>27.7</v>
       </c>
-      <c r="B61" t="n">
+      <c r="B61">
         <v>4</v>
       </c>
-      <c r="C61" t="n">
+      <c r="C61">
         <v>57.3</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D61">
         <v>1.52</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="n">
+    <row r="62" spans="1:4">
+      <c r="A62">
         <v>59.9</v>
       </c>
-      <c r="B62" t="n">
+      <c r="B62">
         <v>10</v>
       </c>
-      <c r="C62" t="n">
+      <c r="C62">
         <v>63.8</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D62">
         <v>1.69</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="n">
+    <row r="63" spans="1:4">
+      <c r="A63">
         <v>19.6</v>
       </c>
-      <c r="B63" t="n">
+      <c r="B63">
         <v>10</v>
       </c>
-      <c r="C63" t="n">
+      <c r="C63">
         <v>70.8</v>
       </c>
-      <c r="D63" t="n">
+      <c r="D63">
         <v>1.81</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="n">
+    <row r="64" spans="1:4">
+      <c r="A64">
         <v>21.8</v>
       </c>
-      <c r="B64" t="n">
+      <c r="B64">
         <v>9</v>
       </c>
-      <c r="C64" t="n">
+      <c r="C64">
         <v>81.09999999999999</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D64">
         <v>1.79</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="n">
+    <row r="65" spans="1:4">
+      <c r="A65">
         <v>26.4</v>
       </c>
-      <c r="B65" t="n">
+      <c r="B65">
         <v>7</v>
       </c>
-      <c r="C65" t="n">
+      <c r="C65">
         <v>97.2</v>
       </c>
-      <c r="D65" t="n">
+      <c r="D65">
         <v>1.57</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="n">
+    <row r="66" spans="1:4">
+      <c r="A66">
         <v>73.90000000000001</v>
       </c>
-      <c r="B66" t="n">
+      <c r="B66">
         <v>2</v>
       </c>
-      <c r="C66" t="n">
+      <c r="C66">
         <v>75.09999999999999</v>
       </c>
-      <c r="D66" t="n">
+      <c r="D66">
         <v>1.65</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="n">
+    <row r="67" spans="1:4">
+      <c r="A67">
         <v>66.5</v>
       </c>
-      <c r="B67" t="n">
+      <c r="B67">
         <v>5</v>
       </c>
-      <c r="C67" t="n">
+      <c r="C67">
         <v>71.7</v>
       </c>
-      <c r="D67" t="n">
+      <c r="D67">
         <v>1.77</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="n">
+    <row r="68" spans="1:4">
+      <c r="A68">
         <v>59</v>
       </c>
-      <c r="B68" t="n">
+      <c r="B68">
         <v>9</v>
       </c>
-      <c r="C68" t="n">
+      <c r="C68">
         <v>82.3</v>
       </c>
-      <c r="D68" t="n">
+      <c r="D68">
         <v>1.86</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="n">
+    <row r="69" spans="1:4">
+      <c r="A69">
         <v>58.3</v>
       </c>
-      <c r="B69" t="n">
+      <c r="B69">
         <v>3</v>
       </c>
-      <c r="C69" t="n">
+      <c r="C69">
         <v>74.3</v>
       </c>
-      <c r="D69" t="n">
+      <c r="D69">
         <v>1.58</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="n">
+    <row r="70" spans="1:4">
+      <c r="A70">
         <v>36.2</v>
       </c>
-      <c r="B70" t="n">
+      <c r="B70">
         <v>7</v>
       </c>
-      <c r="C70" t="n">
+      <c r="C70">
         <v>44.6</v>
       </c>
-      <c r="D70" t="n">
+      <c r="D70">
         <v>1.59</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="n">
+    <row r="71" spans="1:4">
+      <c r="A71">
         <v>50.7</v>
       </c>
-      <c r="B71" t="n">
+      <c r="B71">
         <v>0</v>
       </c>
-      <c r="C71" t="n">
+      <c r="C71">
         <v>61</v>
       </c>
-      <c r="D71" t="n">
+      <c r="D71">
         <v>1.79</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="n">
+    <row r="72" spans="1:4">
+      <c r="A72">
         <v>47.9</v>
       </c>
-      <c r="B72" t="n">
+      <c r="B72">
         <v>7</v>
       </c>
-      <c r="C72" t="n">
+      <c r="C72">
         <v>51.4</v>
       </c>
-      <c r="D72" t="n">
+      <c r="D72">
         <v>1.64</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="n">
+    <row r="73" spans="1:4">
+      <c r="A73">
         <v>77</v>
       </c>
-      <c r="B73" t="n">
+      <c r="B73">
         <v>10</v>
       </c>
-      <c r="C73" t="n">
+      <c r="C73">
         <v>80.40000000000001</v>
       </c>
-      <c r="D73" t="n">
+      <c r="D73">
         <v>1.58</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="n">
+    <row r="74" spans="1:4">
+      <c r="A74">
         <v>46.2</v>
       </c>
-      <c r="B74" t="n">
+      <c r="B74">
         <v>0</v>
       </c>
-      <c r="C74" t="n">
+      <c r="C74">
         <v>89.09999999999999</v>
       </c>
-      <c r="D74" t="n">
+      <c r="D74">
         <v>1.79</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="n">
+    <row r="75" spans="1:4">
+      <c r="A75">
         <v>64.3</v>
       </c>
-      <c r="B75" t="n">
+      <c r="B75">
         <v>10</v>
       </c>
-      <c r="C75" t="n">
+      <c r="C75">
         <v>75.3</v>
       </c>
-      <c r="D75" t="n">
+      <c r="D75">
         <v>1.51</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="n">
+    <row r="76" spans="1:4">
+      <c r="A76">
         <v>40.2</v>
       </c>
-      <c r="B76" t="n">
+      <c r="B76">
         <v>0</v>
       </c>
-      <c r="C76" t="n">
+      <c r="C76">
         <v>54.5</v>
       </c>
-      <c r="D76" t="n">
+      <c r="D76">
         <v>1.61</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="n">
+    <row r="77" spans="1:4">
+      <c r="A77">
         <v>75.40000000000001</v>
       </c>
-      <c r="B77" t="n">
+      <c r="B77">
         <v>10</v>
       </c>
-      <c r="C77" t="n">
+      <c r="C77">
         <v>82</v>
       </c>
-      <c r="D77" t="n">
+      <c r="D77">
         <v>1.78</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="n">
+    <row r="78" spans="1:4">
+      <c r="A78">
         <v>70.8</v>
       </c>
-      <c r="B78" t="n">
+      <c r="B78">
         <v>5</v>
       </c>
-      <c r="C78" t="n">
+      <c r="C78">
         <v>55.5</v>
       </c>
-      <c r="D78" t="n">
+      <c r="D78">
         <v>1.62</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="n">
+    <row r="79" spans="1:4">
+      <c r="A79">
         <v>79.5</v>
       </c>
-      <c r="B79" t="n">
+      <c r="B79">
         <v>5</v>
       </c>
-      <c r="C79" t="n">
+      <c r="C79">
         <v>73.8</v>
       </c>
-      <c r="D79" t="n">
+      <c r="D79">
         <v>1.76</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="n">
+    <row r="80" spans="1:4">
+      <c r="A80">
         <v>32.1</v>
       </c>
-      <c r="B80" t="n">
+      <c r="B80">
         <v>0</v>
       </c>
-      <c r="C80" t="n">
+      <c r="C80">
         <v>52</v>
       </c>
-      <c r="D80" t="n">
+      <c r="D80">
         <v>1.56</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="n">
+    <row r="81" spans="1:4">
+      <c r="A81">
         <v>72</v>
       </c>
-      <c r="B81" t="n">
+      <c r="B81">
         <v>6</v>
       </c>
-      <c r="C81" t="n">
+      <c r="C81">
         <v>49.2</v>
       </c>
-      <c r="D81" t="n">
+      <c r="D81">
         <v>1.76</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="n">
+    <row r="82" spans="1:4">
+      <c r="A82">
         <v>47.6</v>
       </c>
-      <c r="B82" t="n">
+      <c r="B82">
         <v>2</v>
       </c>
-      <c r="C82" t="n">
+      <c r="C82">
         <v>48.9</v>
       </c>
-      <c r="D82" t="n">
+      <c r="D82">
         <v>1.73</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="n">
+    <row r="83" spans="1:4">
+      <c r="A83">
         <v>49.6</v>
       </c>
-      <c r="B83" t="n">
+      <c r="B83">
         <v>3</v>
       </c>
-      <c r="C83" t="n">
+      <c r="C83">
         <v>70.3</v>
       </c>
-      <c r="D83" t="n">
+      <c r="D83">
         <v>1.84</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="n">
+    <row r="84" spans="1:4">
+      <c r="A84">
         <v>51.6</v>
       </c>
-      <c r="B84" t="n">
+      <c r="B84">
         <v>1</v>
       </c>
-      <c r="C84" t="n">
+      <c r="C84">
         <v>60.1</v>
       </c>
-      <c r="D84" t="n">
+      <c r="D84">
         <v>1.66</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="n">
+    <row r="85" spans="1:4">
+      <c r="A85">
         <v>23.7</v>
       </c>
-      <c r="B85" t="n">
+      <c r="B85">
         <v>9</v>
       </c>
-      <c r="C85" t="n">
+      <c r="C85">
         <v>76.5</v>
       </c>
-      <c r="D85" t="n">
+      <c r="D85">
         <v>1.64</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="n">
+    <row r="86" spans="1:4">
+      <c r="A86">
         <v>72.59999999999999</v>
       </c>
-      <c r="B86" t="n">
+      <c r="B86">
         <v>1</v>
       </c>
-      <c r="C86" t="n">
+      <c r="C86">
         <v>50.5</v>
       </c>
-      <c r="D86" t="n">
+      <c r="D86">
         <v>1.67</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="n">
+    <row r="87" spans="1:4">
+      <c r="A87">
         <v>55.5</v>
       </c>
-      <c r="B87" t="n">
+      <c r="B87">
         <v>6</v>
       </c>
-      <c r="C87" t="n">
+      <c r="C87">
         <v>77.40000000000001</v>
       </c>
-      <c r="D87" t="n">
+      <c r="D87">
         <v>1.78</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="n">
+    <row r="88" spans="1:4">
+      <c r="A88">
         <v>24.5</v>
       </c>
-      <c r="B88" t="n">
+      <c r="B88">
         <v>6</v>
       </c>
-      <c r="C88" t="n">
+      <c r="C88">
         <v>60.7</v>
       </c>
-      <c r="D88" t="n">
+      <c r="D88">
         <v>1.61</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="n">
+    <row r="89" spans="1:4">
+      <c r="A89">
         <v>63.8</v>
       </c>
-      <c r="B89" t="n">
+      <c r="B89">
         <v>3</v>
       </c>
-      <c r="C89" t="n">
+      <c r="C89">
         <v>88.8</v>
       </c>
-      <c r="D89" t="n">
+      <c r="D89">
         <v>1.67</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="n">
+    <row r="90" spans="1:4">
+      <c r="A90">
         <v>25</v>
       </c>
-      <c r="B90" t="n">
+      <c r="B90">
         <v>0</v>
       </c>
-      <c r="C90" t="n">
+      <c r="C90">
         <v>85.3</v>
       </c>
-      <c r="D90" t="n">
+      <c r="D90">
         <v>1.87</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="n">
+    <row r="91" spans="1:4">
+      <c r="A91">
         <v>41.6</v>
       </c>
-      <c r="B91" t="n">
+      <c r="B91">
         <v>3</v>
       </c>
-      <c r="C91" t="n">
+      <c r="C91">
         <v>66.8</v>
       </c>
-      <c r="D91" t="n">
+      <c r="D91">
         <v>1.76</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="n">
+    <row r="92" spans="1:4">
+      <c r="A92">
         <v>59.5</v>
       </c>
-      <c r="B92" t="n">
+      <c r="B92">
         <v>2</v>
       </c>
-      <c r="C92" t="n">
+      <c r="C92">
         <v>71.59999999999999</v>
       </c>
-      <c r="D92" t="n">
+      <c r="D92">
         <v>1.75</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="n">
+    <row r="93" spans="1:4">
+      <c r="A93">
         <v>46.8</v>
       </c>
-      <c r="B93" t="n">
+      <c r="B93">
         <v>3</v>
       </c>
-      <c r="C93" t="n">
+      <c r="C93">
         <v>73.7</v>
       </c>
-      <c r="D93" t="n">
+      <c r="D93">
         <v>1.63</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="n">
+    <row r="94" spans="1:4">
+      <c r="A94">
         <v>22</v>
       </c>
-      <c r="B94" t="n">
+      <c r="B94">
         <v>5</v>
       </c>
-      <c r="C94" t="n">
+      <c r="C94">
         <v>77</v>
       </c>
-      <c r="D94" t="n">
+      <c r="D94">
         <v>1.77</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="n">
+    <row r="95" spans="1:4">
+      <c r="A95">
         <v>56.6</v>
       </c>
-      <c r="B95" t="n">
+      <c r="B95">
         <v>7</v>
       </c>
-      <c r="C95" t="n">
+      <c r="C95">
         <v>65.90000000000001</v>
       </c>
-      <c r="D95" t="n">
+      <c r="D95">
         <v>1.56</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="n">
+    <row r="96" spans="1:4">
+      <c r="A96">
         <v>40.7</v>
       </c>
-      <c r="B96" t="n">
+      <c r="B96">
         <v>9</v>
       </c>
-      <c r="C96" t="n">
+      <c r="C96">
         <v>86.40000000000001</v>
       </c>
-      <c r="D96" t="n">
+      <c r="D96">
         <v>1.53</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="n">
+    <row r="97" spans="1:4">
+      <c r="A97">
         <v>41.6</v>
       </c>
-      <c r="B97" t="n">
+      <c r="B97">
         <v>8</v>
       </c>
-      <c r="C97" t="n">
+      <c r="C97">
         <v>62.4</v>
       </c>
-      <c r="D97" t="n">
+      <c r="D97">
         <v>1.59</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="n">
+    <row r="98" spans="1:4">
+      <c r="A98">
         <v>28.1</v>
       </c>
-      <c r="B98" t="n">
+      <c r="B98">
         <v>9</v>
       </c>
-      <c r="C98" t="n">
+      <c r="C98">
         <v>41.1</v>
       </c>
-      <c r="D98" t="n">
+      <c r="D98">
         <v>1.82</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="n">
+    <row r="99" spans="1:4">
+      <c r="A99">
         <v>29.4</v>
       </c>
-      <c r="B99" t="n">
+      <c r="B99">
         <v>1</v>
       </c>
-      <c r="C99" t="n">
+      <c r="C99">
         <v>73.7</v>
       </c>
-      <c r="D99" t="n">
+      <c r="D99">
         <v>1.7</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="n">
+    <row r="100" spans="1:4">
+      <c r="A100">
         <v>79.59999999999999</v>
       </c>
-      <c r="B100" t="n">
+      <c r="B100">
         <v>8</v>
       </c>
-      <c r="C100" t="n">
+      <c r="C100">
         <v>68.40000000000001</v>
       </c>
-      <c r="D100" t="n">
+      <c r="D100">
         <v>1.59</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="n">
+    <row r="101" spans="1:4">
+      <c r="A101">
         <v>55.5</v>
       </c>
-      <c r="B101" t="n">
+      <c r="B101">
         <v>10</v>
       </c>
-      <c r="C101" t="n">
+      <c r="C101">
         <v>82.5</v>
       </c>
-      <c r="D101" t="n">
+      <c r="D101">
         <v>1.64</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>